--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260914.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,293,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
